--- a/output/Itogovaya_otchetnost.xlsx
+++ b/output/Itogovaya_otchetnost.xlsx
@@ -626,7 +626,7 @@
         </is>
       </c>
       <c r="D2" s="3" t="n">
-        <v>185000</v>
+        <v>3850000</v>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
@@ -635,12 +635,12 @@
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>90.1</t>
+          <t>6010</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>Продажи (выручка)</t>
+          <t>Доход от реализации продукции и услуг</t>
         </is>
       </c>
       <c r="H2" s="4" t="inlineStr"/>
@@ -662,7 +662,7 @@
         </is>
       </c>
       <c r="D3" s="3" t="n">
-        <v>42300</v>
+        <v>620000</v>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
@@ -671,12 +671,12 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>90.1</t>
+          <t>6010</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>Продажи (выручка)</t>
+          <t>Доход от реализации продукции и услуг</t>
         </is>
       </c>
       <c r="H3" s="4" t="inlineStr"/>
@@ -698,7 +698,7 @@
         </is>
       </c>
       <c r="D4" s="3" t="n">
-        <v>25000</v>
+        <v>350000</v>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
@@ -707,12 +707,12 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>90.1</t>
+          <t>6010</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>Продажи (выручка)</t>
+          <t>Доход от реализации продукции и услуг</t>
         </is>
       </c>
       <c r="H4" s="4" t="inlineStr"/>
@@ -734,7 +734,7 @@
         </is>
       </c>
       <c r="D5" s="3" t="n">
-        <v>76400</v>
+        <v>1640000</v>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
@@ -743,7 +743,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1350</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
         </is>
       </c>
       <c r="D6" s="3" t="n">
-        <v>18650</v>
+        <v>245000</v>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
@@ -779,12 +779,12 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>7210</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>Общехозяйственные расходы — коммунальные услуги</t>
+          <t>Административные расходы — коммунальные услуги</t>
         </is>
       </c>
       <c r="H6" s="4" t="inlineStr"/>
@@ -806,7 +806,7 @@
         </is>
       </c>
       <c r="D7" s="3" t="n">
-        <v>4200</v>
+        <v>68000</v>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
@@ -815,12 +815,12 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>7210</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>Общехозяйственные расходы — коммунальные услуги</t>
+          <t>Административные расходы — коммунальные услуги</t>
         </is>
       </c>
       <c r="H7" s="4" t="inlineStr"/>
@@ -842,7 +842,7 @@
         </is>
       </c>
       <c r="D8" s="6" t="n">
-        <v>60000</v>
+        <v>850000</v>
       </c>
       <c r="E8" s="5" t="inlineStr">
         <is>
@@ -851,12 +851,12 @@
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>7210</t>
         </is>
       </c>
       <c r="G8" s="5" t="inlineStr">
         <is>
-          <t>Общехозяйственные расходы — аренда</t>
+          <t>Административные расходы — аренда</t>
         </is>
       </c>
       <c r="H8" s="7" t="inlineStr">
@@ -882,7 +882,7 @@
         </is>
       </c>
       <c r="D9" s="6" t="n">
-        <v>60000</v>
+        <v>850000</v>
       </c>
       <c r="E9" s="5" t="inlineStr">
         <is>
@@ -891,12 +891,12 @@
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>7210</t>
         </is>
       </c>
       <c r="G9" s="5" t="inlineStr">
         <is>
-          <t>Общехозяйственные расходы — аренда</t>
+          <t>Административные расходы — аренда</t>
         </is>
       </c>
       <c r="H9" s="7" t="inlineStr">
@@ -922,7 +922,7 @@
         </is>
       </c>
       <c r="D10" s="3" t="n">
-        <v>38900</v>
+        <v>540000</v>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
@@ -931,12 +931,12 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>90.1</t>
+          <t>6010</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>Продажи (выручка)</t>
+          <t>Доход от реализации продукции и услуг</t>
         </is>
       </c>
       <c r="H10" s="4" t="inlineStr"/>
@@ -958,7 +958,7 @@
         </is>
       </c>
       <c r="D11" s="3" t="n">
-        <v>15300</v>
+        <v>210000</v>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
@@ -967,12 +967,12 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>7110</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>Расходы на продажу — транспорт</t>
+          <t>Расходы по реализации — транспорт</t>
         </is>
       </c>
       <c r="H11" s="4" t="inlineStr"/>
@@ -990,11 +990,11 @@
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>Зарплата за август 2026 (5 сотрудников по 45 000 тенге)</t>
+          <t>Зарплата за август 2026 (5 сотрудников по 350 000 тенге)</t>
         </is>
       </c>
       <c r="D12" s="6" t="n">
-        <v>205000</v>
+        <v>1550000</v>
       </c>
       <c r="E12" s="5" t="inlineStr">
         <is>
@@ -1003,17 +1003,17 @@
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>3350</t>
         </is>
       </c>
       <c r="G12" s="5" t="inlineStr">
         <is>
-          <t>Расчёты с персоналом по оплате труда</t>
+          <t>Краткосрочная задолженность по оплате труда</t>
         </is>
       </c>
       <c r="H12" s="7" t="inlineStr">
         <is>
-          <t>Сумма не соответствует расчёту в назначении платежа: по тексту ожидается 225 000 ₸, а указано 205 000 ₸ (расхождение 20 000 ₸). Требуется уточнить сумму у бухгалтера.</t>
+          <t>Сумма не соответствует расчёту в назначении платежа: по тексту ожидается 1 750 000 ₸, а указано 1 550 000 ₸ (расхождение 200 000 ₸). Требуется уточнить сумму у бухгалтера.</t>
         </is>
       </c>
     </row>
@@ -1030,11 +1030,11 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>Перечислены страховые взносы с ФОТ за июль 2026</t>
+          <t>Перечислены социальные отчисления и взносы с ФОТ за июль 2026</t>
         </is>
       </c>
       <c r="D13" s="3" t="n">
-        <v>67500</v>
+        <v>315000</v>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
@@ -1043,12 +1043,12 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>69</t>
+          <t>3220</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>Расчёты по социальному страхованию</t>
+          <t>Обязательства по социальному страхованию</t>
         </is>
       </c>
       <c r="H13" s="4" t="inlineStr"/>
@@ -1070,7 +1070,7 @@
         </is>
       </c>
       <c r="D14" s="3" t="n">
-        <v>8200</v>
+        <v>95000</v>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
@@ -1079,12 +1079,12 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>7210</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>Общехозяйственные расходы — охрана</t>
+          <t>Административные расходы — охрана</t>
         </is>
       </c>
       <c r="H14" s="4" t="inlineStr"/>
@@ -1106,7 +1106,7 @@
         </is>
       </c>
       <c r="D15" s="3" t="n">
-        <v>182000</v>
+        <v>2950000</v>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
@@ -1115,12 +1115,12 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>90.1</t>
+          <t>6010</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>Продажи (выручка)</t>
+          <t>Доход от реализации продукции и услуг</t>
         </is>
       </c>
       <c r="H15" s="4" t="inlineStr"/>
@@ -1142,7 +1142,7 @@
         </is>
       </c>
       <c r="D16" s="3" t="n">
-        <v>22000</v>
+        <v>380000</v>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
@@ -1151,12 +1151,12 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>7110</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>Расходы на продажу — реклама</t>
+          <t>Расходы по реализации — реклама</t>
         </is>
       </c>
       <c r="H16" s="4" t="inlineStr"/>
@@ -1178,7 +1178,7 @@
         </is>
       </c>
       <c r="D17" s="3" t="n">
-        <v>3100</v>
+        <v>42000</v>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
@@ -1187,12 +1187,12 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>7210</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>Общехозяйственные расходы — банковские услуги</t>
+          <t>Административные расходы — банковские услуги</t>
         </is>
       </c>
       <c r="H17" s="4" t="inlineStr"/>
@@ -1214,7 +1214,7 @@
         </is>
       </c>
       <c r="D18" s="3" t="n">
-        <v>51200</v>
+        <v>710000</v>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
@@ -1223,12 +1223,12 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>90.1</t>
+          <t>6010</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>Продажи (выручка)</t>
+          <t>Доход от реализации продукции и услуг</t>
         </is>
       </c>
       <c r="H18" s="4" t="inlineStr"/>
@@ -1250,7 +1250,7 @@
         </is>
       </c>
       <c r="D19" s="3" t="n">
-        <v>4850</v>
+        <v>78000</v>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
@@ -1259,12 +1259,12 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>7210</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>Общехозяйственные расходы — канцтовары</t>
+          <t>Административные расходы — канцтовары</t>
         </is>
       </c>
       <c r="H19" s="4" t="inlineStr"/>
@@ -1286,7 +1286,7 @@
         </is>
       </c>
       <c r="D20" s="3" t="n">
-        <v>9700</v>
+        <v>130000</v>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
@@ -1295,12 +1295,12 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>7210</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>Общехозяйственные расходы — ремонт</t>
+          <t>Административные расходы — ремонт</t>
         </is>
       </c>
       <c r="H20" s="4" t="inlineStr"/>
@@ -1318,11 +1318,11 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>Уплачен налог по УСН (авансовый платёж за 3 квартал 2026)</t>
+          <t>Уплачен налог по упрощённой декларации СНР (авансовый платёж за 3 квартал 2026)</t>
         </is>
       </c>
       <c r="D21" s="3" t="n">
-        <v>48000</v>
+        <v>620000</v>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
@@ -1331,12 +1331,12 @@
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>68</t>
+          <t>3110</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>Расчёты по налогам и сборам</t>
+          <t>Расчёты по налогам (КПН/СНР)</t>
         </is>
       </c>
       <c r="H21" s="4" t="inlineStr"/>
@@ -1358,7 +1358,7 @@
         </is>
       </c>
       <c r="D22" s="3" t="n">
-        <v>11200</v>
+        <v>175000</v>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
@@ -1367,12 +1367,12 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>66</t>
+          <t>7310</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>Расчёты по кредитам и займам</t>
+          <t>Расходы по вознаграждениям — проценты по кредиту</t>
         </is>
       </c>
       <c r="H22" s="4" t="inlineStr"/>
@@ -1394,7 +1394,7 @@
         </is>
       </c>
       <c r="D23" s="3" t="n">
-        <v>96500</v>
+        <v>1680000</v>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
@@ -1403,12 +1403,12 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>90.1</t>
+          <t>6010</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>Продажи (выручка)</t>
+          <t>Доход от реализации продукции и услуг</t>
         </is>
       </c>
       <c r="H23" s="4" t="inlineStr"/>
@@ -1430,7 +1430,7 @@
         </is>
       </c>
       <c r="D24" s="3" t="n">
-        <v>5400</v>
+        <v>65000</v>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
@@ -1439,12 +1439,12 @@
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>7210</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>Общехозяйственные расходы — связь</t>
+          <t>Административные расходы — связь</t>
         </is>
       </c>
       <c r="H24" s="4" t="inlineStr"/>
@@ -1498,11 +1498,11 @@
     <row r="5">
       <c r="A5" s="11" t="inlineStr">
         <is>
-          <t>Продажи (выручка)</t>
+          <t>Доход от реализации продукции и услуг</t>
         </is>
       </c>
       <c r="B5" s="12" t="n">
-        <v>620900</v>
+        <v>10700000</v>
       </c>
     </row>
     <row r="6">
@@ -1526,11 +1526,11 @@
     <row r="9">
       <c r="A9" s="11" t="inlineStr">
         <is>
-          <t>Расчёты с персоналом по оплате труда</t>
+          <t>Краткосрочная задолженность по оплате труда</t>
         </is>
       </c>
       <c r="B9" s="12" t="n">
-        <v>225000</v>
+        <v>1750000</v>
       </c>
     </row>
     <row r="10">
@@ -1540,127 +1540,127 @@
         </is>
       </c>
       <c r="B10" s="12" t="n">
-        <v>76400</v>
+        <v>1640000</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="11" t="inlineStr">
         <is>
-          <t>Расчёты по социальному страхованию</t>
+          <t>Административные расходы — аренда</t>
         </is>
       </c>
       <c r="B11" s="12" t="n">
-        <v>67500</v>
+        <v>850000</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="11" t="inlineStr">
         <is>
-          <t>Общехозяйственные расходы — аренда</t>
+          <t>Расчёты по налогам (КПН/СНР)</t>
         </is>
       </c>
       <c r="B12" s="12" t="n">
-        <v>60000</v>
+        <v>620000</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="11" t="inlineStr">
         <is>
-          <t>Расчёты по налогам и сборам</t>
+          <t>Расходы по реализации — реклама</t>
         </is>
       </c>
       <c r="B13" s="12" t="n">
-        <v>48000</v>
+        <v>380000</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="11" t="inlineStr">
         <is>
-          <t>Общехозяйственные расходы — коммунальные услуги</t>
+          <t>Обязательства по социальному страхованию</t>
         </is>
       </c>
       <c r="B14" s="12" t="n">
-        <v>22850</v>
+        <v>315000</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="11" t="inlineStr">
         <is>
-          <t>Расходы на продажу — реклама</t>
+          <t>Административные расходы — коммунальные услуги</t>
         </is>
       </c>
       <c r="B15" s="12" t="n">
-        <v>22000</v>
+        <v>313000</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="11" t="inlineStr">
         <is>
-          <t>Расходы на продажу — транспорт</t>
+          <t>Расходы по реализации — транспорт</t>
         </is>
       </c>
       <c r="B16" s="12" t="n">
-        <v>15300</v>
+        <v>210000</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="11" t="inlineStr">
         <is>
-          <t>Расчёты по кредитам и займам</t>
+          <t>Расходы по вознаграждениям — проценты по кредиту</t>
         </is>
       </c>
       <c r="B17" s="12" t="n">
-        <v>11200</v>
+        <v>175000</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="11" t="inlineStr">
         <is>
-          <t>Общехозяйственные расходы — ремонт</t>
+          <t>Административные расходы — ремонт</t>
         </is>
       </c>
       <c r="B18" s="12" t="n">
-        <v>9700</v>
+        <v>130000</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="11" t="inlineStr">
         <is>
-          <t>Общехозяйственные расходы — охрана</t>
+          <t>Административные расходы — охрана</t>
         </is>
       </c>
       <c r="B19" s="12" t="n">
-        <v>8200</v>
+        <v>95000</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="11" t="inlineStr">
         <is>
-          <t>Общехозяйственные расходы — связь</t>
+          <t>Административные расходы — канцтовары</t>
         </is>
       </c>
       <c r="B20" s="12" t="n">
-        <v>5400</v>
+        <v>78000</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="11" t="inlineStr">
         <is>
-          <t>Общехозяйственные расходы — канцтовары</t>
+          <t>Административные расходы — связь</t>
         </is>
       </c>
       <c r="B21" s="12" t="n">
-        <v>4850</v>
+        <v>65000</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="11" t="inlineStr">
         <is>
-          <t>Общехозяйственные расходы — банковские услуги</t>
+          <t>Административные расходы — банковские услуги</t>
         </is>
       </c>
       <c r="B22" s="12" t="n">
-        <v>3100</v>
+        <v>42000</v>
       </c>
     </row>
     <row r="23">
@@ -1688,7 +1688,7 @@
     <row r="28">
       <c r="A28" s="8" t="inlineStr">
         <is>
-          <t>Справочно: без учёта проверки ИИ (с задвоенным платежом и ошибкой в сумме зарплаты) финансовый результат составил бы 1 400 ₸.</t>
+          <t>Справочно: без учёта проверки ИИ (с задвоенным платежом и ошибкой в сумме зарплаты) финансовый результат составил бы 3 387 000 ₸.</t>
         </is>
       </c>
     </row>
@@ -1738,7 +1738,7 @@
         </is>
       </c>
       <c r="B5" s="12" t="n">
-        <v>150000</v>
+        <v>2500000</v>
       </c>
     </row>
     <row r="6">
@@ -1788,7 +1788,7 @@
         </is>
       </c>
       <c r="B11" s="12" t="n">
-        <v>150000</v>
+        <v>2500000</v>
       </c>
     </row>
     <row r="12">
@@ -1880,7 +1880,7 @@
     <row r="7" ht="18" customHeight="1">
       <c r="A7" s="21" t="inlineStr">
         <is>
-          <t>За август 2026 года компания «Светлый Дом» получила выручку в размере 620 900 ₸ — в основном за счёт оптовых продаж товаров и розничной торговли, а также разовых консультационных услуг. Расходы компании за тот же период составили 579 500 ₸ и включают оплату труда сотрудников, аренду офиса, закупку материалов, коммунальные и налоговые платежи, а также услуги сторонних организаций (реклама, охрана, банк, связь).</t>
+          <t>За август 2026 года компания «Светлый Дом» получила выручку в размере 10 700 000 ₸ — в основном за счёт оптовых продаж товаров и розничной торговли, а также разовых консультационных услуг. Расходы компании за тот же период составили 6 663 000 ₸ и включают оплату труда сотрудников, аренду офиса, закупку материалов, коммунальные и налоговые платежи, а также услуги сторонних организаций (реклама, охрана, банк, связь).</t>
         </is>
       </c>
     </row>
@@ -1890,7 +1890,7 @@
     <row r="9" ht="18" customHeight="1">
       <c r="A9" s="21" t="inlineStr">
         <is>
-          <t>По итогам месяца финансовый результат компании — прибыль в размере 41 400 ₸. Остаток денежных средств на конец месяца составил 191 400 ₸ (при остатке 150 000 ₸ на начало месяца). Эта сумма отражена в упрощённом балансе как денежные средства в активе и как собственный капитал (с учётом прибыли месяца) в пассиве — баланс сходится.</t>
+          <t>По итогам месяца финансовый результат компании — прибыль в размере 4 037 000 ₸. Остаток денежных средств на конец месяца составил 6 537 000 ₸ (при остатке 2 500 000 ₸ на начало месяца). Эта сумма отражена в упрощённом балансе как денежные средства в активе и как собственный капитал (с учётом прибыли месяца) в пассиве — баланс сходится.</t>
         </is>
       </c>
     </row>
@@ -1900,7 +1900,7 @@
     <row r="11" ht="18" customHeight="1">
       <c r="A11" s="21" t="inlineStr">
         <is>
-          <t>При автоматической проверке данных ИИ-сервис обнаружил один задвоенный платёж (одна и та же операция ошибочно повторяется в таблице дважды) и 1 операцию, где указанная сумма не совпадала с расчётом, приведённым в самом назначении платежа. Если бы эти ошибки не были замечены и исправлены, итоговый финансовый результат месяца показал бы прибыль всего 1 400 ₸ — то есть отчётность вводила бы в заблуждение примерно на 40 000 ₸. Это наглядно показывает, зачем нужна проверка первичных данных перед составлением отчётности, и как в этом может помочь ИИ.</t>
+          <t>При автоматической проверке данных ИИ-сервис обнаружил один задвоенный платёж (одна и та же операция ошибочно повторяется в таблице дважды) и 1 операцию, где указанная сумма не совпадала с расчётом, приведённым в самом назначении платежа. Если бы эти ошибки не были замечены и исправлены, итоговый финансовый результат месяца показал бы прибыль всего 3 387 000 ₸ — то есть отчётность вводила бы в заблуждение примерно на 650 000 ₸. Это наглядно показывает, зачем нужна проверка первичных данных перед составлением отчётности, и как в этом может помочь ИИ.</t>
         </is>
       </c>
     </row>
